--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742581</v>
+        <v>122742582</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Sanddals- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739527</v>
+        <v>739447</v>
       </c>
       <c r="R2" t="n">
-        <v>7148887</v>
+        <v>7148913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742582</v>
+        <v>122742581</v>
       </c>
       <c r="B3" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddals- NV, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739447</v>
+        <v>739527</v>
       </c>
       <c r="R3" t="n">
-        <v>7148913</v>
+        <v>7148887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742582</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122742581</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742582</v>
+        <v>122742581</v>
       </c>
       <c r="B2" t="n">
         <v>90962</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- NV, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739447</v>
+        <v>739527</v>
       </c>
       <c r="R2" t="n">
-        <v>7148913</v>
+        <v>7148887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742581</v>
+        <v>122742582</v>
       </c>
       <c r="B3" t="n">
         <v>90962</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Sanddals- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739527</v>
+        <v>739447</v>
       </c>
       <c r="R3" t="n">
-        <v>7148887</v>
+        <v>7148913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742581</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122742582</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742581</v>
+        <v>122742582</v>
       </c>
       <c r="B2" t="n">
         <v>90970</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Sanddals- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739527</v>
+        <v>739447</v>
       </c>
       <c r="R2" t="n">
-        <v>7148887</v>
+        <v>7148913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742582</v>
+        <v>122742581</v>
       </c>
       <c r="B3" t="n">
         <v>90970</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddals- NV, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739447</v>
+        <v>739527</v>
       </c>
       <c r="R3" t="n">
-        <v>7148913</v>
+        <v>7148887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742582</v>
+        <v>122742581</v>
       </c>
       <c r="B2" t="n">
         <v>90970</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- NV, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739447</v>
+        <v>739527</v>
       </c>
       <c r="R2" t="n">
-        <v>7148913</v>
+        <v>7148887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742581</v>
+        <v>122742582</v>
       </c>
       <c r="B3" t="n">
         <v>90970</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Sanddals- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739527</v>
+        <v>739447</v>
       </c>
       <c r="R3" t="n">
-        <v>7148887</v>
+        <v>7148913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742581</v>
+        <v>122742582</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Sanddals- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739527</v>
+        <v>739447</v>
       </c>
       <c r="R2" t="n">
-        <v>7148887</v>
+        <v>7148913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742582</v>
+        <v>122742581</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddals- NV, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739447</v>
+        <v>739527</v>
       </c>
       <c r="R3" t="n">
-        <v>7148913</v>
+        <v>7148887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 57484-2021 artfynd.xlsx
+++ b/artfynd/A 57484-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742582</v>
+        <v>122742581</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- NV, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739447</v>
+        <v>739527</v>
       </c>
       <c r="R2" t="n">
-        <v>7148913</v>
+        <v>7148887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742581</v>
+        <v>122742582</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Sanddals- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739527</v>
+        <v>739447</v>
       </c>
       <c r="R3" t="n">
-        <v>7148887</v>
+        <v>7148913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
